--- a/reports_excel/張希慈執行長主管專用_【主管評下屬用】.xlsx
+++ b/reports_excel/張希慈執行長主管專用_【主管評下屬用】.xlsx
@@ -205,9 +205,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -263,6 +260,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -710,19 +710,11 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>部屬自評</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>主管評定</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
           <t>主管評核回饋與觀察</t>
         </is>
       </c>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -740,13 +732,13 @@
           <t>進行部門招募時策略、執行與協調都能夠獨立完成，同時協調其他部門需求，確保招募目標符合所有人想像。</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
     </row>
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -764,13 +756,13 @@
           <t>酷童工作人員徽章製作時有一些分歧，在決定權上也有些模糊的地方，但我能夠主動提出自己的想法，同時也了解他人的需求後共同產出符合所有人想像的成果。</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="54" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -788,13 +780,13 @@
           <t>在新的兼職入職後，給予他們方向與目標的指示，其他時候根據他們個人的理解讓他們自行發揮，而並非要求所有事情按照我制定的規則來。而後我會給予最低限度的建議與方向修正，這對我而言是一種接納多元工作方法的表現。</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
     </row>
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -812,18 +804,18 @@
           <t>因懷孕不適，有不出門辦公的需求，也因此會產生許多仰賴同事的狀況。過往習慣自己把事情都做好，今年則是把自己能夠處理的部分以及能在其他方面彌補他人工作量的地方先規劃好，再學著如何請同事協助。與喻翔曾經有因為請求他協助而有一些摩擦的狀況，但是在彼此溝通後發現彼此之間都有一些沒溝通清楚的地方，經過溝通後最後也讓任務順利完成。</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>二、專業職能：自評 vs 主管評分並列對照【品牌經理】（逐項比對認知差異）</t>
+          <t>二、專業職能：自評 vs 主管評分並列對照【$品牌經理】（逐項比對認知差異）</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -865,7 +857,7 @@
       </c>
     </row>
     <row r="12" ht="72" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>品牌定位與外部溝通一致性</t>
         </is>
@@ -888,19 +880,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="13" ht="90" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>行銷策略與議題倡議</t>
         </is>
@@ -923,19 +915,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="14" ht="72" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>品牌活動策劃與策展敘事</t>
         </is>
@@ -958,19 +950,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="15" ht="72" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>內部品牌管理與雇主品牌</t>
         </is>
@@ -993,19 +985,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="16" ht="72" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>品牌危機與聲譽風險處理</t>
         </is>
@@ -1028,166 +1020,171 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="10">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="D7:F7"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="A10:F10"/>
+    <mergeCell ref="D5:F5"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D4:F4"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="E12 E13 E14 E15 E16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="評分無效" error="請從選單選擇等級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" promptTitle="等級選單" prompt="請選取評級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" type="list">
@@ -1232,7 +1229,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>評估對象：胡喻翔（專案經理） ｜ 直屬主管：張希慈 ｜ 同儕填答樣本：4 位 ｜ 自評狀態：尚未自評</t>
+          <t>評估對象：胡喻翔（專案經理） ｜ 直屬主管：張希慈 ｜ 同儕填答樣本：$4 位 ｜ 自評狀態：$尚未自評</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1293,12 +1290,12 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Q24</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>合作狀況</t>
         </is>
@@ -1308,28 +1305,28 @@
           <t>合作狀況（溝通順暢度、資訊透明度、承諾事項達成率）</t>
         </is>
       </c>
-      <c r="D5" s="25" t="n">
+      <c r="D5" s="24" t="n">
         <v>9.5</v>
       </c>
-      <c r="E5" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F5" s="6" t="n">
+      <c r="E5" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>9.0, 10.0, 10.0, 9.0</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Q25</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>工作品質</t>
         </is>
@@ -1339,28 +1336,28 @@
           <t>注重細節（工作成果之品質與細緻度）</t>
         </is>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="24" t="n">
         <v>9.75</v>
       </c>
-      <c r="E6" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F6" s="6" t="n">
+      <c r="E6" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0, 9.0</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>Q26</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>專案進度</t>
         </is>
@@ -1370,28 +1367,28 @@
           <t>準時完成（專案進度與時程掌控）</t>
         </is>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="24" t="n">
         <v>9.75</v>
       </c>
-      <c r="E7" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" s="6" t="n">
+      <c r="E7" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0, 9.0</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Q27</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>變動彈性</t>
         </is>
@@ -1401,28 +1398,28 @@
           <t>靈活調整（面對臨時變動與突發狀況的彈性）</t>
         </is>
       </c>
-      <c r="D8" s="25" t="n">
+      <c r="D8" s="24" t="n">
         <v>9.25</v>
       </c>
-      <c r="E8" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F8" s="6" t="n">
+      <c r="E8" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>9.0, 9.0, 10.0, 9.0</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Q28</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>追蹤承諾</t>
         </is>
@@ -1432,28 +1429,28 @@
           <t>追蹤承諾（主動回報進度與承諾事項追蹤）</t>
         </is>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="24" t="n">
         <v>9.75</v>
       </c>
-      <c r="E9" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" s="6" t="n">
+      <c r="E9" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0, 9.0</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>Q29</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>透明溝通</t>
         </is>
@@ -1463,16 +1460,16 @@
           <t>說明決策依據（決策與工作方法透明度）</t>
         </is>
       </c>
-      <c r="D10" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="D10" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0, 10.0</t>
         </is>
@@ -1494,16 +1491,16 @@
           <t>【多元】接受不同意見（能開放聆聽反對觀點）</t>
         </is>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="E11" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F11" s="6" t="n">
+      <c r="E11" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="25" t="inlineStr">
         <is>
           <t>10.0, 9.0, 10.0, 7.0</t>
         </is>
@@ -1525,16 +1522,16 @@
           <t>【多元】提出建設性觀點（在討論中給予實質建議）</t>
         </is>
       </c>
-      <c r="D12" s="25" t="n">
+      <c r="D12" s="24" t="n">
         <v>9.5</v>
       </c>
-      <c r="E12" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F12" s="6" t="n">
+      <c r="E12" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0, 8.0</t>
         </is>
@@ -1556,16 +1553,16 @@
           <t>【實驗】開放調整（透過回饋持續迭代優化）</t>
         </is>
       </c>
-      <c r="D13" s="25" t="n">
+      <c r="D13" s="24" t="n">
         <v>9.75</v>
       </c>
-      <c r="E13" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" s="6" t="n">
+      <c r="E13" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0, 9.0</t>
         </is>
@@ -1587,16 +1584,16 @@
           <t>【信任】分享經驗與資源（主動協助夥伴）</t>
         </is>
       </c>
-      <c r="D14" s="25" t="n">
+      <c r="D14" s="24" t="n">
         <v>9.75</v>
       </c>
-      <c r="E14" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F14" s="6" t="n">
+      <c r="E14" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0, 9.0</t>
         </is>
@@ -1618,16 +1615,16 @@
           <t>【可持續】讚美與肯定同儕（經常給予夥伴正向激勵）</t>
         </is>
       </c>
-      <c r="D15" s="25" t="n">
+      <c r="D15" s="24" t="n">
         <v>9.33</v>
       </c>
-      <c r="E15" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F15" s="6" t="n">
+      <c r="E15" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="25" t="inlineStr">
         <is>
           <t>9.0, 9.0, 10.0</t>
         </is>
@@ -1649,28 +1646,28 @@
           <t>【可持續】尊重工作界線（維護彼此身心健康與邊界）</t>
         </is>
       </c>
-      <c r="D16" s="25" t="n">
+      <c r="D16" s="24" t="n">
         <v>9.67</v>
       </c>
-      <c r="E16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F16" s="6" t="n">
+      <c r="E16" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="25" t="inlineStr">
         <is>
           <t>9.0, 10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>Q36</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>NPS推薦</t>
         </is>
@@ -1680,16 +1677,16 @@
           <t>NPS 推薦度（向他人推薦與此夥伴共事的意願）</t>
         </is>
       </c>
-      <c r="D17" s="25" t="n">
+      <c r="D17" s="24" t="n">
         <v>9.33</v>
       </c>
-      <c r="E17" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F17" s="6" t="n">
+      <c r="E17" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t>9.0, 9.0, 10.0</t>
         </is>
@@ -2236,142 +2233,142 @@
       <c r="G48" s="5" t="n"/>
     </row>
     <row r="50" ht="24" customHeight="1">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B50" s="10" t="n"/>
-      <c r="C50" s="10" t="n"/>
-      <c r="D50" s="10" t="n"/>
+      <c r="B50" s="9" t="n"/>
+      <c r="C50" s="9" t="n"/>
+      <c r="D50" s="9" t="n"/>
     </row>
     <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="11" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B51" s="11" t="inlineStr">
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C51" s="11" t="inlineStr">
+      <c r="C51" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D51" s="11" t="inlineStr">
+      <c r="D51" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1">
-      <c r="A52" s="12" t="inlineStr">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="B52" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C52" s="14" t="inlineStr">
+      <c r="C52" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D52" s="14" t="inlineStr">
+      <c r="D52" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="53" ht="28" customHeight="1">
-      <c r="A53" s="15" t="inlineStr">
+      <c r="A53" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B53" s="16" t="inlineStr">
+      <c r="B53" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C53" s="17" t="inlineStr">
+      <c r="C53" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D53" s="17" t="inlineStr">
+      <c r="D53" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="54" ht="28" customHeight="1">
-      <c r="A54" s="18" t="inlineStr">
+      <c r="A54" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B54" s="19" t="inlineStr">
+      <c r="B54" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C54" s="20" t="inlineStr">
+      <c r="C54" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D54" s="20" t="inlineStr">
+      <c r="D54" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1">
-      <c r="A55" s="21" t="inlineStr">
+      <c r="A55" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B55" s="22" t="inlineStr">
+      <c r="B55" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C55" s="23" t="inlineStr">
+      <c r="C55" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D55" s="23" t="inlineStr">
+      <c r="D55" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
-      <c r="A56" s="21" t="inlineStr">
+      <c r="A56" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B56" s="22" t="inlineStr">
+      <c r="B56" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C56" s="23" t="inlineStr">
+      <c r="C56" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D56" s="23" t="inlineStr">
+      <c r="D56" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
@@ -2452,7 +2449,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>評估對象：何維安（品牌經理） ｜ 直屬主管：張希慈 ｜ 同儕填答樣本：2 位 ｜ 自評狀態：已自評</t>
+          <t>評估對象：何維安（品牌經理） ｜ 直屬主管：張希慈 ｜ 同儕填答樣本：$2 位 ｜ 自評狀態：$已自評</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2513,12 +2510,12 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Q24</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>合作狀況</t>
         </is>
@@ -2528,28 +2525,28 @@
           <t>合作狀況（溝通順暢度、資訊透明度、承諾事項達成率）</t>
         </is>
       </c>
-      <c r="D5" s="25" t="n">
+      <c r="D5" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="E5" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F5" s="6" t="n">
+      <c r="E5" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>10.0, 8.0</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Q25</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>工作品質</t>
         </is>
@@ -2559,28 +2556,28 @@
           <t>注重細節（工作成果之品質與細緻度）</t>
         </is>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="24" t="n">
         <v>8.5</v>
       </c>
-      <c r="E6" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F6" s="6" t="n">
+      <c r="E6" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="25" t="inlineStr">
         <is>
           <t>10.0, 7.0</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>Q26</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>專案進度</t>
         </is>
@@ -2590,28 +2587,28 @@
           <t>準時完成（專案進度與時程掌控）</t>
         </is>
       </c>
-      <c r="D7" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="D7" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Q27</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>變動彈性</t>
         </is>
@@ -2621,28 +2618,28 @@
           <t>靈活調整（面對臨時變動與突發狀況的彈性）</t>
         </is>
       </c>
-      <c r="D8" s="25" t="n">
+      <c r="D8" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="E8" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F8" s="6" t="n">
+      <c r="E8" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>10.0, 8.0</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Q28</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>追蹤承諾</t>
         </is>
@@ -2652,28 +2649,28 @@
           <t>追蹤承諾（主動回報進度與承諾事項追蹤）</t>
         </is>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="24" t="n">
         <v>9.5</v>
       </c>
-      <c r="E9" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" s="6" t="n">
+      <c r="E9" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t>10.0, 9.0</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>Q29</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>透明溝通</t>
         </is>
@@ -2683,16 +2680,16 @@
           <t>說明決策依據（決策與工作方法透明度）</t>
         </is>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="24" t="n">
         <v>8.5</v>
       </c>
-      <c r="E10" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F10" s="6" t="n">
+      <c r="E10" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t>10.0, 7.0</t>
         </is>
@@ -2714,16 +2711,16 @@
           <t>【多元】接受不同意見（能開放聆聽反對觀點）</t>
         </is>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="24" t="n">
         <v>8.5</v>
       </c>
-      <c r="E11" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F11" s="6" t="n">
+      <c r="E11" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="25" t="inlineStr">
         <is>
           <t>10.0, 7.0</t>
         </is>
@@ -2745,16 +2742,16 @@
           <t>【多元】提出建設性觀點（在討論中給予實質建議）</t>
         </is>
       </c>
-      <c r="D12" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="D12" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
@@ -2776,16 +2773,16 @@
           <t>【實驗】開放調整（透過回饋持續迭代優化）</t>
         </is>
       </c>
-      <c r="D13" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="D13" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
@@ -2807,16 +2804,16 @@
           <t>【信任】分享經驗與資源（主動協助夥伴）</t>
         </is>
       </c>
-      <c r="D14" s="25" t="n">
+      <c r="D14" s="24" t="n">
         <v>9.5</v>
       </c>
-      <c r="E14" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F14" s="6" t="n">
+      <c r="E14" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="25" t="inlineStr">
         <is>
           <t>10.0, 9.0</t>
         </is>
@@ -2838,16 +2835,16 @@
           <t>【可持續】讚美與肯定同儕（經常給予夥伴正向激勵）</t>
         </is>
       </c>
-      <c r="D15" s="25" t="n">
+      <c r="D15" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="25" t="inlineStr">
         <is>
           <t>9.0, 9.0</t>
         </is>
@@ -2869,28 +2866,28 @@
           <t>【可持續】尊重工作界線（維護彼此身心健康與邊界）</t>
         </is>
       </c>
-      <c r="D16" s="25" t="n">
+      <c r="D16" s="24" t="n">
         <v>8.5</v>
       </c>
-      <c r="E16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F16" s="6" t="n">
+      <c r="E16" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="25" t="inlineStr">
         <is>
           <t>10.0, 7.0</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>Q36</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>NPS推薦</t>
         </is>
@@ -2900,16 +2897,16 @@
           <t>NPS 推薦度（向他人推薦與此夥伴共事的意願）</t>
         </is>
       </c>
-      <c r="D17" s="25" t="n">
+      <c r="D17" s="24" t="n">
         <v>9.5</v>
       </c>
-      <c r="E17" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F17" s="6" t="n">
+      <c r="E17" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t>10.0, 9.0</t>
         </is>
@@ -3353,142 +3350,142 @@
       <c r="G42" s="5" t="n"/>
     </row>
     <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
+      <c r="B44" s="9" t="n"/>
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="9" t="n"/>
     </row>
     <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="11" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D45" s="11" t="inlineStr">
+      <c r="D45" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="12" t="inlineStr">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B46" s="13" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C46" s="14" t="inlineStr">
+      <c r="C46" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D46" s="14" t="inlineStr">
+      <c r="D46" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B47" s="16" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C47" s="17" t="inlineStr">
+      <c r="C47" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D47" s="17" t="inlineStr">
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="18" t="inlineStr">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B48" s="19" t="inlineStr">
+      <c r="B48" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C48" s="20" t="inlineStr">
+      <c r="C48" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D48" s="20" t="inlineStr">
+      <c r="D48" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="21" t="inlineStr">
+      <c r="A49" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B49" s="22" t="inlineStr">
+      <c r="B49" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C49" s="23" t="inlineStr">
+      <c r="C49" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D49" s="23" t="inlineStr">
+      <c r="D49" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="21" t="inlineStr">
+      <c r="A50" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B50" s="22" t="inlineStr">
+      <c r="B50" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C50" s="23" t="inlineStr">
+      <c r="C50" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D50" s="23" t="inlineStr">
+      <c r="D50" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
@@ -3600,19 +3597,11 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>部屬自評</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>主管評定</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
           <t>主管評核回饋與觀察</t>
         </is>
       </c>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5" ht="90" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -3631,13 +3620,13 @@
 遇到我不理解的問題(可能是請款、法規或業務工作等等)，我自己會主動先搜尋相關資料，若是無法有明確的答案，會與相關夥伴或會計詢問。</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -3655,13 +3644,13 @@
           <t>當討論事情(像是週會討論事項或是品牌跨部門會議)，我也會表達自己的觀點及建議給夥伴們參考，也接納不同的建議及想法，尊重每位夥伴的觀點。</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="54" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -3679,13 +3668,13 @@
           <t>今年有更多的使用AI來協作工作，像是董事會會議紀錄有先請AI幫我整理，我再做整體調整！請款部分目前還在嘗試有沒有AI可以讓工作流程更順暢的部分。</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
     </row>
     <row r="8" ht="72" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -3704,18 +3693,18 @@
 我自己平時就會平衡工作與生活，今年也開始做瑜珈運動，做好自我照顧！</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>二、專業職能：自評 vs 主管評分並列對照【行政經理】（逐項比對認知差異）</t>
+          <t>二、專業職能：自評 vs 主管評分並列對照【$行政經理】（逐項比對認知差異）</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -3757,7 +3746,7 @@
       </c>
     </row>
     <row r="12" ht="72" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>人事薪資與人資系統管理</t>
         </is>
@@ -3781,19 +3770,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="13" ht="72" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>法規與政府公文管理</t>
         </is>
@@ -3817,19 +3806,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>董事會與治理作業執行</t>
         </is>
@@ -3853,19 +3842,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>財務核銷與內控執行</t>
         </is>
@@ -3891,19 +3880,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>總務採購與行政庶務管理</t>
         </is>
@@ -3929,166 +3918,171 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="10">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="D7:F7"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="A10:F10"/>
+    <mergeCell ref="D5:F5"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D4:F4"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="E12 E13 E14 E15 E16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="評分無效" error="請從選單選擇等級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" promptTitle="等級選單" prompt="請選取評級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" type="list">
@@ -4133,7 +4127,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>評估對象：陳泳璇（行政經理） ｜ 直屬主管：張希慈 ｜ 同儕填答樣本：2 位 ｜ 自評狀態：已自評</t>
+          <t>評估對象：陳泳璇（行政經理） ｜ 直屬主管：張希慈 ｜ 同儕填答樣本：$2 位 ｜ 自評狀態：$已自評</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -4194,12 +4188,12 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Q24</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>合作狀況</t>
         </is>
@@ -4209,28 +4203,28 @@
           <t>合作狀況（溝通順暢度、資訊透明度、承諾事項達成率）</t>
         </is>
       </c>
-      <c r="D5" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="D5" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Q25</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>工作品質</t>
         </is>
@@ -4240,28 +4234,28 @@
           <t>注重細節（工作成果之品質與細緻度）</t>
         </is>
       </c>
-      <c r="D6" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="D6" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>Q26</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>專案進度</t>
         </is>
@@ -4271,28 +4265,28 @@
           <t>準時完成（專案進度與時程掌控）</t>
         </is>
       </c>
-      <c r="D7" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="D7" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Q27</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>變動彈性</t>
         </is>
@@ -4302,28 +4296,28 @@
           <t>靈活調整（面對臨時變動與突發狀況的彈性）</t>
         </is>
       </c>
-      <c r="D8" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="D8" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Q28</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>追蹤承諾</t>
         </is>
@@ -4333,28 +4327,28 @@
           <t>追蹤承諾（主動回報進度與承諾事項追蹤）</t>
         </is>
       </c>
-      <c r="D9" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="D9" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>Q29</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>透明溝通</t>
         </is>
@@ -4364,16 +4358,16 @@
           <t>說明決策依據（決策與工作方法透明度）</t>
         </is>
       </c>
-      <c r="D10" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="D10" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
@@ -4395,16 +4389,16 @@
           <t>【多元】接受不同意見（能開放聆聽反對觀點）</t>
         </is>
       </c>
-      <c r="D11" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="D11" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
@@ -4426,16 +4420,16 @@
           <t>【多元】提出建設性觀點（在討論中給予實質建議）</t>
         </is>
       </c>
-      <c r="D12" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="D12" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
@@ -4457,16 +4451,16 @@
           <t>【實驗】開放調整（透過回饋持續迭代優化）</t>
         </is>
       </c>
-      <c r="D13" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="D13" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
@@ -4488,16 +4482,16 @@
           <t>【信任】分享經驗與資源（主動協助夥伴）</t>
         </is>
       </c>
-      <c r="D14" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="D14" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
@@ -4519,16 +4513,16 @@
           <t>【可持續】讚美與肯定同儕（經常給予夥伴正向激勵）</t>
         </is>
       </c>
-      <c r="D15" s="25" t="n">
+      <c r="D15" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="E15" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F15" s="6" t="n">
+      <c r="E15" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="25" t="inlineStr">
         <is>
           <t>8.0, 10.0</t>
         </is>
@@ -4550,28 +4544,28 @@
           <t>【可持續】尊重工作界線（維護彼此身心健康與邊界）</t>
         </is>
       </c>
-      <c r="D16" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="D16" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>Q36</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>NPS推薦</t>
         </is>
@@ -4581,16 +4575,16 @@
           <t>NPS 推薦度（向他人推薦與此夥伴共事的意願）</t>
         </is>
       </c>
-      <c r="D17" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="D17" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
@@ -5044,142 +5038,142 @@
       <c r="G42" s="5" t="n"/>
     </row>
     <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
+      <c r="B44" s="9" t="n"/>
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="9" t="n"/>
     </row>
     <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="11" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D45" s="11" t="inlineStr">
+      <c r="D45" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="12" t="inlineStr">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B46" s="13" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C46" s="14" t="inlineStr">
+      <c r="C46" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D46" s="14" t="inlineStr">
+      <c r="D46" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B47" s="16" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C47" s="17" t="inlineStr">
+      <c r="C47" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D47" s="17" t="inlineStr">
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="18" t="inlineStr">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B48" s="19" t="inlineStr">
+      <c r="B48" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C48" s="20" t="inlineStr">
+      <c r="C48" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D48" s="20" t="inlineStr">
+      <c r="D48" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="21" t="inlineStr">
+      <c r="A49" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B49" s="22" t="inlineStr">
+      <c r="B49" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C49" s="23" t="inlineStr">
+      <c r="C49" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D49" s="23" t="inlineStr">
+      <c r="D49" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="21" t="inlineStr">
+      <c r="A50" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B50" s="22" t="inlineStr">
+      <c r="B50" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C50" s="23" t="inlineStr">
+      <c r="C50" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D50" s="23" t="inlineStr">
+      <c r="D50" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
@@ -5291,19 +5285,11 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>部屬自評</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>主管評定</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
           <t>主管評核回饋與觀察</t>
         </is>
       </c>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -5321,13 +5307,13 @@
           <t>（部屬未填寫）</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -5345,13 +5331,13 @@
           <t>（部屬未填寫）</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -5369,13 +5355,13 @@
           <t>（部屬未填寫）</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -5393,18 +5379,18 @@
           <t>（部屬未填寫）</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>二、專業職能：自評 vs 主管評分並列對照【營運經理兼執行長特助】（逐項比對認知差異）</t>
+          <t>二、專業職能：自評 vs 主管評分並列對照【$營運經理兼執行長特助】（逐項比對認知差異）</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -5446,7 +5432,7 @@
       </c>
     </row>
     <row r="12" ht="90" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>組織營運流程設計與優化</t>
         </is>
@@ -5470,19 +5456,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="13" ht="90" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>制度文件與 SOP 建置</t>
         </is>
@@ -5505,19 +5491,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>人力資源策略與選用育留</t>
         </is>
@@ -5541,19 +5527,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>員工關係處理與勞動合規</t>
         </is>
@@ -5576,19 +5562,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>組織文化落實與制度轉化</t>
         </is>
@@ -5611,166 +5597,171 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="10">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="D7:F7"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="A10:F10"/>
+    <mergeCell ref="D5:F5"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D4:F4"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="E12 E13 E14 E15 E16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="評分無效" error="請從選單選擇等級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" promptTitle="等級選單" prompt="請選取評級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" type="list">
@@ -5815,7 +5806,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>評估對象：張芳媐（營運經理兼執行長特助） ｜ 直屬主管：張希慈 ｜ 同儕填答樣本：4 位 ｜ 自評狀態：尚未自評</t>
+          <t>評估對象：張芳媐（營運經理兼執行長特助） ｜ 直屬主管：張希慈 ｜ 同儕填答樣本：$4 位 ｜ 自評狀態：$尚未自評</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -5876,12 +5867,12 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Q24</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>合作狀況</t>
         </is>
@@ -5891,28 +5882,28 @@
           <t>合作狀況（溝通順暢度、資訊透明度、承諾事項達成率）</t>
         </is>
       </c>
-      <c r="D5" s="25" t="n">
+      <c r="D5" s="24" t="n">
         <v>9.75</v>
       </c>
-      <c r="E5" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F5" s="6" t="n">
+      <c r="E5" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 9.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Q25</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>工作品質</t>
         </is>
@@ -5922,28 +5913,28 @@
           <t>注重細節（工作成果之品質與細緻度）</t>
         </is>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="24" t="n">
         <v>8.25</v>
       </c>
-      <c r="E6" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F6" s="6" t="n">
+      <c r="E6" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="25" t="inlineStr">
         <is>
           <t>10.0, 9.0, 6.0, 8.0</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>Q26</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>專案進度</t>
         </is>
@@ -5953,28 +5944,28 @@
           <t>準時完成（專案進度與時程掌控）</t>
         </is>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="24" t="n">
         <v>9.5</v>
       </c>
-      <c r="E7" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" s="6" t="n">
+      <c r="E7" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 9.0, 9.0</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Q27</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>變動彈性</t>
         </is>
@@ -5984,28 +5975,28 @@
           <t>靈活調整（面對臨時變動與突發狀況的彈性）</t>
         </is>
       </c>
-      <c r="D8" s="25" t="n">
+      <c r="D8" s="24" t="n">
         <v>9.75</v>
       </c>
-      <c r="E8" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F8" s="6" t="n">
+      <c r="E8" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 9.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Q28</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>追蹤承諾</t>
         </is>
@@ -6015,28 +6006,28 @@
           <t>追蹤承諾（主動回報進度與承諾事項追蹤）</t>
         </is>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="24" t="n">
         <v>9.75</v>
       </c>
-      <c r="E9" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" s="6" t="n">
+      <c r="E9" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 9.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>Q29</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>透明溝通</t>
         </is>
@@ -6046,16 +6037,16 @@
           <t>說明決策依據（決策與工作方法透明度）</t>
         </is>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="24" t="n">
         <v>9.25</v>
       </c>
-      <c r="E10" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F10" s="6" t="n">
+      <c r="E10" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 7.0, 10.0</t>
         </is>
@@ -6077,16 +6068,16 @@
           <t>【多元】接受不同意見（能開放聆聽反對觀點）</t>
         </is>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="24" t="n">
         <v>9.75</v>
       </c>
-      <c r="E11" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F11" s="6" t="n">
+      <c r="E11" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 9.0, 10.0</t>
         </is>
@@ -6108,16 +6099,16 @@
           <t>【多元】提出建設性觀點（在討論中給予實質建議）</t>
         </is>
       </c>
-      <c r="D12" s="25" t="n">
+      <c r="D12" s="24" t="n">
         <v>9.25</v>
       </c>
-      <c r="E12" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F12" s="6" t="n">
+      <c r="E12" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 9.0, 8.0</t>
         </is>
@@ -6139,16 +6130,16 @@
           <t>【實驗】開放調整（透過回饋持續迭代優化）</t>
         </is>
       </c>
-      <c r="D13" s="25" t="n">
+      <c r="D13" s="24" t="n">
         <v>9.75</v>
       </c>
-      <c r="E13" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" s="6" t="n">
+      <c r="E13" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 9.0, 10.0</t>
         </is>
@@ -6170,16 +6161,16 @@
           <t>【信任】分享經驗與資源（主動協助夥伴）</t>
         </is>
       </c>
-      <c r="D14" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="D14" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0, 10.0</t>
         </is>
@@ -6201,16 +6192,16 @@
           <t>【可持續】讚美與肯定同儕（經常給予夥伴正向激勵）</t>
         </is>
       </c>
-      <c r="D15" s="25" t="n">
+      <c r="D15" s="24" t="n">
         <v>9.75</v>
       </c>
-      <c r="E15" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F15" s="6" t="n">
+      <c r="E15" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 9.0, 10.0</t>
         </is>
@@ -6232,28 +6223,28 @@
           <t>【可持續】尊重工作界線（維護彼此身心健康與邊界）</t>
         </is>
       </c>
-      <c r="D16" s="25" t="n">
+      <c r="D16" s="24" t="n">
         <v>9.75</v>
       </c>
-      <c r="E16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F16" s="6" t="n">
+      <c r="E16" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 9.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>Q36</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>NPS推薦</t>
         </is>
@@ -6263,16 +6254,16 @@
           <t>NPS 推薦度（向他人推薦與此夥伴共事的意願）</t>
         </is>
       </c>
-      <c r="D17" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="D17" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
@@ -6817,142 +6808,142 @@
       <c r="G48" s="5" t="n"/>
     </row>
     <row r="50" ht="24" customHeight="1">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B50" s="10" t="n"/>
-      <c r="C50" s="10" t="n"/>
-      <c r="D50" s="10" t="n"/>
+      <c r="B50" s="9" t="n"/>
+      <c r="C50" s="9" t="n"/>
+      <c r="D50" s="9" t="n"/>
     </row>
     <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="11" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B51" s="11" t="inlineStr">
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C51" s="11" t="inlineStr">
+      <c r="C51" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D51" s="11" t="inlineStr">
+      <c r="D51" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1">
-      <c r="A52" s="12" t="inlineStr">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="B52" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C52" s="14" t="inlineStr">
+      <c r="C52" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D52" s="14" t="inlineStr">
+      <c r="D52" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="53" ht="28" customHeight="1">
-      <c r="A53" s="15" t="inlineStr">
+      <c r="A53" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B53" s="16" t="inlineStr">
+      <c r="B53" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C53" s="17" t="inlineStr">
+      <c r="C53" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D53" s="17" t="inlineStr">
+      <c r="D53" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="54" ht="28" customHeight="1">
-      <c r="A54" s="18" t="inlineStr">
+      <c r="A54" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B54" s="19" t="inlineStr">
+      <c r="B54" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C54" s="20" t="inlineStr">
+      <c r="C54" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D54" s="20" t="inlineStr">
+      <c r="D54" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1">
-      <c r="A55" s="21" t="inlineStr">
+      <c r="A55" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B55" s="22" t="inlineStr">
+      <c r="B55" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C55" s="23" t="inlineStr">
+      <c r="C55" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D55" s="23" t="inlineStr">
+      <c r="D55" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
-      <c r="A56" s="21" t="inlineStr">
+      <c r="A56" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B56" s="22" t="inlineStr">
+      <c r="B56" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C56" s="23" t="inlineStr">
+      <c r="C56" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D56" s="23" t="inlineStr">
+      <c r="D56" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
@@ -7070,19 +7061,11 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>部屬自評</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>主管評定</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
           <t>主管評核回饋與觀察</t>
         </is>
       </c>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -7100,13 +7083,13 @@
           <t>（部屬未填寫）</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -7124,13 +7107,13 @@
           <t>（部屬未填寫）</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -7148,13 +7131,13 @@
           <t>（部屬未填寫）</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -7172,18 +7155,18 @@
           <t>（部屬未填寫）</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>二、專業職能：自評 vs 主管評分並列對照【部門儲備主管】（逐項比對認知差異）</t>
+          <t>二、專業職能：自評 vs 主管評分並列對照【$部門儲備主管】（逐項比對認知差異）</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -7225,7 +7208,7 @@
       </c>
     </row>
     <row r="12" ht="90" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>部門策略規劃與專案組合管理</t>
         </is>
@@ -7248,19 +7231,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="13" ht="108" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>專案經理管理與培育</t>
         </is>
@@ -7283,19 +7266,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="14" ht="72" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>部門預算與資源配置管理</t>
         </is>
@@ -7318,19 +7301,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="15" ht="126" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>跨 LAB 專業掌握（CGL 教育專業與 SL 社群培力）</t>
         </is>
@@ -7353,19 +7336,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>利害關係人管理與衝突協調</t>
         </is>
@@ -7388,166 +7371,171 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="10">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="D7:F7"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="A10:F10"/>
+    <mergeCell ref="D5:F5"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D4:F4"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="E12 E13 E14 E15 E16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="評分無效" error="請從選單選擇等級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" promptTitle="等級選單" prompt="請選取評級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" type="list">
@@ -7592,7 +7580,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>評估對象：姚品瑄（部門儲備主管） ｜ 直屬主管：張希慈 ｜ 同儕填答樣本：3 位 ｜ 自評狀態：尚未自評</t>
+          <t>評估對象：姚品瑄（部門儲備主管） ｜ 直屬主管：張希慈 ｜ 同儕填答樣本：$3 位 ｜ 自評狀態：$尚未自評</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -7653,12 +7641,12 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Q24</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>合作狀況</t>
         </is>
@@ -7668,28 +7656,28 @@
           <t>合作狀況（溝通順暢度、資訊透明度、承諾事項達成率）</t>
         </is>
       </c>
-      <c r="D5" s="25" t="n">
+      <c r="D5" s="24" t="n">
         <v>9.67</v>
       </c>
-      <c r="E5" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F5" s="6" t="n">
+      <c r="E5" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>9.0, 10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Q25</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>工作品質</t>
         </is>
@@ -7699,28 +7687,28 @@
           <t>注重細節（工作成果之品質與細緻度）</t>
         </is>
       </c>
-      <c r="D6" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="D6" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>Q26</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>專案進度</t>
         </is>
@@ -7730,28 +7718,28 @@
           <t>準時完成（專案進度與時程掌控）</t>
         </is>
       </c>
-      <c r="D7" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="D7" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Q27</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>變動彈性</t>
         </is>
@@ -7761,28 +7749,28 @@
           <t>靈活調整（面對臨時變動與突發狀況的彈性）</t>
         </is>
       </c>
-      <c r="D8" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="D8" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Q28</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>追蹤承諾</t>
         </is>
@@ -7792,28 +7780,28 @@
           <t>追蹤承諾（主動回報進度與承諾事項追蹤）</t>
         </is>
       </c>
-      <c r="D9" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="D9" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>Q29</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>透明溝通</t>
         </is>
@@ -7823,16 +7811,16 @@
           <t>說明決策依據（決策與工作方法透明度）</t>
         </is>
       </c>
-      <c r="D10" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="D10" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
@@ -7854,16 +7842,16 @@
           <t>【多元】接受不同意見（能開放聆聽反對觀點）</t>
         </is>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="24" t="n">
         <v>9.33</v>
       </c>
-      <c r="E11" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F11" s="6" t="n">
+      <c r="E11" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="25" t="inlineStr">
         <is>
           <t>9.0, 9.0, 10.0</t>
         </is>
@@ -7885,16 +7873,16 @@
           <t>【多元】提出建設性觀點（在討論中給予實質建議）</t>
         </is>
       </c>
-      <c r="D12" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="D12" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
@@ -7916,16 +7904,16 @@
           <t>【實驗】開放調整（透過回饋持續迭代優化）</t>
         </is>
       </c>
-      <c r="D13" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="D13" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
@@ -7947,16 +7935,16 @@
           <t>【信任】分享經驗與資源（主動協助夥伴）</t>
         </is>
       </c>
-      <c r="D14" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="D14" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
@@ -7978,16 +7966,16 @@
           <t>【可持續】讚美與肯定同儕（經常給予夥伴正向激勵）</t>
         </is>
       </c>
-      <c r="D15" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="D15" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
@@ -8009,28 +7997,28 @@
           <t>【可持續】尊重工作界線（維護彼此身心健康與邊界）</t>
         </is>
       </c>
-      <c r="D16" s="25" t="n">
+      <c r="D16" s="24" t="n">
         <v>9.67</v>
       </c>
-      <c r="E16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F16" s="6" t="n">
+      <c r="E16" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="25" t="inlineStr">
         <is>
           <t>9.0, 10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>Q36</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>NPS推薦</t>
         </is>
@@ -8040,16 +8028,16 @@
           <t>NPS 推薦度（向他人推薦與此夥伴共事的意願）</t>
         </is>
       </c>
-      <c r="D17" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="D17" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
@@ -8546,142 +8534,142 @@
       <c r="G45" s="5" t="n"/>
     </row>
     <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B47" s="10" t="n"/>
-      <c r="C47" s="10" t="n"/>
-      <c r="D47" s="10" t="n"/>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="9" t="n"/>
     </row>
     <row r="48" ht="24" customHeight="1">
-      <c r="A48" s="11" t="inlineStr">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B48" s="11" t="inlineStr">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C48" s="11" t="inlineStr">
+      <c r="C48" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D48" s="11" t="inlineStr">
+      <c r="D48" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="12" t="inlineStr">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B49" s="13" t="inlineStr">
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C49" s="14" t="inlineStr">
+      <c r="C49" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D49" s="14" t="inlineStr">
+      <c r="D49" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="15" t="inlineStr">
+      <c r="A50" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B50" s="16" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C50" s="17" t="inlineStr">
+      <c r="C50" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D50" s="17" t="inlineStr">
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="51" ht="28" customHeight="1">
-      <c r="A51" s="18" t="inlineStr">
+      <c r="A51" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B51" s="19" t="inlineStr">
+      <c r="B51" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C51" s="20" t="inlineStr">
+      <c r="C51" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D51" s="20" t="inlineStr">
+      <c r="D51" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1">
-      <c r="A52" s="21" t="inlineStr">
+      <c r="A52" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B52" s="22" t="inlineStr">
+      <c r="B52" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C52" s="23" t="inlineStr">
+      <c r="C52" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D52" s="23" t="inlineStr">
+      <c r="D52" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="53" ht="28" customHeight="1">
-      <c r="A53" s="21" t="inlineStr">
+      <c r="A53" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B53" s="22" t="inlineStr">
+      <c r="B53" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C53" s="23" t="inlineStr">
+      <c r="C53" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D53" s="23" t="inlineStr">
+      <c r="D53" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
@@ -8796,19 +8784,11 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>部屬自評</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>主管評定</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
           <t>主管評核回饋與觀察</t>
         </is>
       </c>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -8826,13 +8806,13 @@
           <t>（部屬未填寫）</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -8850,13 +8830,13 @@
           <t>（部屬未填寫）</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -8874,13 +8854,13 @@
           <t>（部屬未填寫）</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -8898,18 +8878,18 @@
           <t>（部屬未填寫）</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>二、專業職能：自評 vs 主管評分並列對照【專案經理】（逐項比對認知差異）</t>
+          <t>二、專業職能：自評 vs 主管評分並列對照【$專案經理】（逐項比對認知差異）</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -8951,7 +8931,7 @@
       </c>
     </row>
     <row r="12" ht="126" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>專案企劃與現場執行</t>
         </is>
@@ -8973,19 +8953,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="13" ht="108" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>專案時程與預算規劃管理</t>
         </is>
@@ -9008,19 +8988,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="14" ht="108" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>需求研究與方案迭代</t>
         </is>
@@ -9042,19 +9022,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="15" ht="108" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>外部夥伴關係經營</t>
         </is>
@@ -9077,19 +9057,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="16" ht="126" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>多元教學設計與現場引導</t>
         </is>
@@ -9114,166 +9094,171 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="10">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="D7:F7"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="A10:F10"/>
+    <mergeCell ref="D5:F5"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D4:F4"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="E12 E13 E14 E15 E16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="評分無效" error="請從選單選擇等級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" promptTitle="等級選單" prompt="請選取評級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" type="list">
